--- a/outputs/tables/tab1_descriptive.xlsx
+++ b/outputs/tables/tab1_descriptive.xlsx
@@ -6,7 +6,7 @@
     <workbookView xWindow="0" yWindow="0" windowWidth="13125" windowHeight="6105" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Tabla" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Table" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
 </workbook>
 </file>
@@ -14,7 +14,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="180">
   <si>
-    <t xml:space="preserve">Tabla 1. Evolución anual de los subsidios a combustibles fósiles (2015-2023)</t>
+    <t xml:space="preserve">Table 1. Annual evolution of fossil fuel subsidies (2015–2023)</t>
   </si>
   <si>
     <t xml:space="preserve">Variable</t>
@@ -47,13 +47,13 @@
     <t xml:space="preserve">2023</t>
   </si>
   <si>
-    <t xml:space="preserve">Panel A. Total LATAM</t>
+    <t xml:space="preserve">Panel A. LAC total</t>
   </si>
   <si>
     <t xml:space="preserve"/>
   </si>
   <si>
-    <t xml:space="preserve">  Explícito (USD bn)</t>
+    <t xml:space="preserve">  Explicit (USD billion)</t>
   </si>
   <si>
     <t xml:space="preserve">55.9</t>
@@ -83,7 +83,7 @@
     <t xml:space="preserve">41.3</t>
   </si>
   <si>
-    <t xml:space="preserve">  Implícito (USD bn)</t>
+    <t xml:space="preserve">  Implicit (USD billion)</t>
   </si>
   <si>
     <t xml:space="preserve">192.4</t>
@@ -113,7 +113,7 @@
     <t xml:space="preserve">231.6</t>
   </si>
   <si>
-    <t xml:space="preserve">  Total (USD bn)</t>
+    <t xml:space="preserve">  Total (USD billion)</t>
   </si>
   <si>
     <t xml:space="preserve">265.3</t>
@@ -143,7 +143,7 @@
     <t xml:space="preserve">290.0</t>
   </si>
   <si>
-    <t xml:space="preserve">  Explícito (% PIB)</t>
+    <t xml:space="preserve">  Explicit (% of GDP)</t>
   </si>
   <si>
     <t xml:space="preserve">0.85</t>
@@ -170,7 +170,7 @@
     <t xml:space="preserve">0.68</t>
   </si>
   <si>
-    <t xml:space="preserve">  Implícito (% PIB)</t>
+    <t xml:space="preserve">  Implicit (% of GDP)</t>
   </si>
   <si>
     <t xml:space="preserve">2.91</t>
@@ -200,7 +200,7 @@
     <t xml:space="preserve">3.81</t>
   </si>
   <si>
-    <t xml:space="preserve">  Total (% PIB)</t>
+    <t xml:space="preserve">  Total (% of GDP)</t>
   </si>
   <si>
     <t xml:space="preserve">4.02</t>
@@ -227,13 +227,13 @@
     <t xml:space="preserve">4.77</t>
   </si>
   <si>
-    <t xml:space="preserve">  N (países)</t>
+    <t xml:space="preserve">  N (countries)</t>
   </si>
   <si>
     <t xml:space="preserve">34</t>
   </si>
   <si>
-    <t xml:space="preserve">Panel B. Exportadores netos de hidrocarburos</t>
+    <t xml:space="preserve">Panel B. Net oil exporters</t>
   </si>
   <si>
     <t xml:space="preserve">37.8</t>
@@ -392,7 +392,7 @@
     <t xml:space="preserve">7</t>
   </si>
   <si>
-    <t xml:space="preserve">Panel C. Importadores netos</t>
+    <t xml:space="preserve">Panel C. Net oil importers</t>
   </si>
   <si>
     <t xml:space="preserve">18.1</t>
@@ -551,7 +551,7 @@
     <t xml:space="preserve">27</t>
   </si>
   <si>
-    <t xml:space="preserve">Notas. Subsidios a combustibles fósiles en América Latina y el Caribe, por año y grupo de exposición, alrededor del choque petrolero de 2022. Cada celda es la suma del grupo en el año: en USD miles de millones (USD bn) y como porcentaje del PIB agregado del grupo. El subsidio explícito mide la brecha entre el precio al consumidor y el costo de suministro; el implícito recoge las externalidades no internalizadas y el IVA no aplicado; el total es la suma de ambos. El explícito es el componente que reacciona al choque en el corto plazo; el implícito depende del volumen consumido y de parámetros de daño ambiental, no del precio internacional. El implícito (y, por tanto, el total) no está estimado para todos los país-año. La clasificación es por exposición fiscal neta al precio del petróleo, no por producción: en los exportadores netos el alza del Brent infla la renta petrolera que financia el subsidio, mientras que en los importadores netos encarece el costo de suministro y agrava el gasto en subsidios. Argentina (importador neto de energía en el período) y Brasil (importa los derivados refinados que se subsidian) se clasifican como importadores. Panel A, Total LATAM (N = 34 países). Panel B, exportadores netos de hidrocarburos (N = 7): Bolivia, Colombia, Ecuador, Guyana, México, Trinidad y Tobago y Venezuela. Panel C, importadores netos (N = 27): Antigua y Barbuda, Argentina, Aruba, Bahamas, Barbados, Belice, Brasil, Chile, Costa Rica, Dominica, El Salvador, Granada, Guatemala, Haití, Honduras, Jamaica, Nicaragua, Panamá, Paraguay, Perú, Puerto Rico, República Dominicana, San Cristóbal y Nieves, San Vicente y las Granadinas, Santa Lucía, Surinam, Uruguay. Fuente: IMF Fossil Fuel Subsidies Database.</t>
+    <t xml:space="preserve">Notes. Group totals by year, in USD billion and as a percentage of the group's aggregate GDP. Explicit: gap between the supply cost and the consumer price. Implicit: uninternalized externalities and forgone VAT, driven mainly by volumes and damage parameters but not independent of the price (its forgone-VAT part scales with it); not estimated for every country-year. Total: the IMF's own aggregate, which need not equal explicit plus implicit. Countries are classified by net oil trade position, not by production. Net oil exporters (seven): Bolivia, Colombia, Ecuador, Guyana, Mexico, Trinidad and Tobago, and Venezuela; the other 27 countries are net oil importers. Source: IMF Fossil Fuel Subsidies Database.</t>
   </si>
 </sst>
 </file>
@@ -1787,7 +1787,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="27" ht="137.5" customHeight="1">
+    <row r="27" ht="62.5" customHeight="1">
       <c r="B27" s="11" t="s">
         <v>179</v>
       </c>

--- a/outputs/tables/tab1_descriptive.xlsx
+++ b/outputs/tables/tab1_descriptive.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="180">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="176">
   <si>
     <t xml:space="preserve">Table 1. Annual evolution of fossil fuel subsidies (2015–2023)</t>
   </si>
@@ -236,322 +236,310 @@
     <t xml:space="preserve">Panel B. Net oil exporters</t>
   </si>
   <si>
-    <t xml:space="preserve">37.8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5</t>
+    <t xml:space="preserve">27.7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2</t>
   </si>
   <si>
     <t xml:space="preserve">28.3</t>
   </si>
   <si>
-    <t xml:space="preserve">54.0</t>
+    <t xml:space="preserve">21.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">78.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">69.9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">73.3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">77.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">79.7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">69.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100.7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">107.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">96.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">111.6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">96.7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">102.7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">109.9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">105.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">83.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">117.6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">136.8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">115.9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.92</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.74</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.49</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.60</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.67</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.91</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.54</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Panel C. Net oil importers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5</t>
   </si>
   <si>
     <t xml:space="preserve">24.0</t>
   </si>
   <si>
+    <t xml:space="preserve">33.8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">113.9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">127.6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">124.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">127.8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">124.4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">123.6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">174.6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">135.6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">153.8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">161.9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">154.6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">165.6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">147.2</t>
+  </si>
+  <si>
     <t xml:space="preserve">110.9</t>
   </si>
   <si>
-    <t xml:space="preserve">117.3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">110.3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">106.4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">97.9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">71.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">131.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">149.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">152.3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">149.8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">156.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">127.8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">127.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">195.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">140.5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.77</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.81</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.52</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.92</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.65</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.42</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.88</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.46</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.69</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.82</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.65</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Panel C. Net oil importers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">80.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">98.5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">106.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87.8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">135.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">151.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">125.3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">116.3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">106.3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">107.4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">119.3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">124.5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">101.5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">161.6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">183.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">149.5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.42</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.29</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.55</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.66</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.44</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.78</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Notes. Group totals by year, in USD billion and as a percentage of the group's aggregate GDP. Explicit: gap between the supply cost and the consumer price. Implicit: uninternalized externalities and forgone VAT, driven mainly by volumes and damage parameters but not independent of the price (its forgone-VAT part scales with it); not estimated for every country-year. Total: the IMF's own aggregate, which need not equal explicit plus implicit. Countries are classified by net oil trade position, not by production. Net oil exporters (seven): Bolivia, Colombia, Ecuador, Guyana, Mexico, Trinidad and Tobago, and Venezuela; the other 27 countries are net oil importers. Source: IMF Fossil Fuel Subsidies Database.</t>
+    <t xml:space="preserve">171.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">241.3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">174.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.78</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.38</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.69</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.84</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.55</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.93</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Notes. Group totals by year, in USD billion and as a percentage of the group's aggregate GDP. Explicit: gap between the supply cost and the consumer price. Implicit: uninternalized externalities and forgone VAT, driven mainly by volumes and damage parameters but not independent of the price (its forgone-VAT part scales with it); not estimated for every country-year. Total: the IMF's own aggregate, which need not equal explicit plus implicit. Countries are classified by net oil trade position (average 2015–2019 net exports of crude oil and refined products, UN Comtrade), not by production. Net oil exporters (five): Brazil, Colombia, Ecuador, Trinidad and Tobago, and Venezuela; the other 29 countries are net oil importers. Source: IMF Fossil Fuel Subsidies Database; UN Comtrade.</t>
   </si>
 </sst>
 </file>
@@ -1368,7 +1356,7 @@
         <v>90</v>
       </c>
       <c r="K13" s="4" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
     </row>
     <row r="14">
@@ -1376,31 +1364,31 @@
         <v>33</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="I14" s="4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="J14" s="4" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="K14" s="4" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="15">
@@ -1408,31 +1396,31 @@
         <v>43</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F15" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="G15" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="G15" s="4" t="s">
+      <c r="H15" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="H15" s="4" t="s">
+      <c r="I15" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="I15" s="4" t="s">
+      <c r="J15" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="J15" s="4" t="s">
+      <c r="K15" s="4" t="s">
         <v>106</v>
-      </c>
-      <c r="K15" s="4" t="s">
-        <v>107</v>
       </c>
     </row>
     <row r="16">
@@ -1440,31 +1428,31 @@
         <v>52</v>
       </c>
       <c r="C16" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="D16" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="D16" s="4" t="s">
+      <c r="E16" s="4" t="s">
         <v>109</v>
       </c>
-      <c r="E16" s="4" t="s">
+      <c r="F16" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="F16" s="4" t="s">
+      <c r="G16" s="4" t="s">
         <v>111</v>
       </c>
-      <c r="G16" s="4" t="s">
+      <c r="H16" s="4" t="s">
         <v>112</v>
       </c>
-      <c r="H16" s="4" t="s">
+      <c r="I16" s="4" t="s">
         <v>113</v>
       </c>
-      <c r="I16" s="4" t="s">
+      <c r="J16" s="4" t="s">
         <v>114</v>
       </c>
-      <c r="J16" s="4" t="s">
+      <c r="K16" s="4" t="s">
         <v>115</v>
-      </c>
-      <c r="K16" s="4" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="17">
@@ -1472,22 +1460,22 @@
         <v>62</v>
       </c>
       <c r="C17" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="D17" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="D17" s="4" t="s">
+      <c r="E17" s="4" t="s">
         <v>118</v>
       </c>
-      <c r="E17" s="4" t="s">
+      <c r="F17" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="F17" s="4" t="s">
+      <c r="G17" s="4" t="s">
         <v>120</v>
       </c>
-      <c r="G17" s="4" t="s">
+      <c r="H17" s="4" t="s">
         <v>121</v>
-      </c>
-      <c r="H17" s="4" t="s">
-        <v>116</v>
       </c>
       <c r="I17" s="4" t="s">
         <v>122</v>
@@ -1504,31 +1492,31 @@
         <v>71</v>
       </c>
       <c r="C18" s="10" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D18" s="10" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E18" s="10" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F18" s="10" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G18" s="10" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H18" s="10" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I18" s="10" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J18" s="10" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K18" s="10" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19">
@@ -1667,28 +1655,28 @@
         <v>154</v>
       </c>
       <c r="D23" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="E23" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="F23" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="G23" s="4" t="s">
         <v>155</v>
       </c>
-      <c r="E23" s="4" t="s">
+      <c r="H23" s="4" t="s">
         <v>156</v>
       </c>
-      <c r="F23" s="4" t="s">
+      <c r="I23" s="4" t="s">
         <v>157</v>
       </c>
-      <c r="G23" s="4" t="s">
-        <v>157</v>
-      </c>
-      <c r="H23" s="4" t="s">
+      <c r="J23" s="4" t="s">
         <v>158</v>
       </c>
-      <c r="I23" s="4" t="s">
+      <c r="K23" s="4" t="s">
         <v>159</v>
-      </c>
-      <c r="J23" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="K23" s="4" t="s">
-        <v>161</v>
       </c>
     </row>
     <row r="24">
@@ -1696,31 +1684,31 @@
         <v>52</v>
       </c>
       <c r="C24" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="D24" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="E24" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="F24" s="4" t="s">
         <v>162</v>
       </c>
-      <c r="D24" s="4" t="s">
+      <c r="G24" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="H24" s="4" t="s">
         <v>163</v>
       </c>
-      <c r="E24" s="4" t="s">
+      <c r="I24" s="4" t="s">
         <v>164</v>
       </c>
-      <c r="F24" s="4" t="s">
+      <c r="J24" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="K24" s="4" t="s">
         <v>165</v>
-      </c>
-      <c r="G24" s="4" t="s">
-        <v>166</v>
-      </c>
-      <c r="H24" s="4" t="s">
-        <v>166</v>
-      </c>
-      <c r="I24" s="4" t="s">
-        <v>167</v>
-      </c>
-      <c r="J24" s="4" t="s">
-        <v>168</v>
-      </c>
-      <c r="K24" s="4" t="s">
-        <v>169</v>
       </c>
     </row>
     <row r="25">
@@ -1728,31 +1716,31 @@
         <v>62</v>
       </c>
       <c r="C25" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="D25" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="E25" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="F25" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="G25" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="H25" s="4" t="s">
         <v>170</v>
       </c>
-      <c r="D25" s="4" t="s">
-        <v>166</v>
-      </c>
-      <c r="E25" s="4" t="s">
+      <c r="I25" s="4" t="s">
         <v>171</v>
       </c>
-      <c r="F25" s="4" t="s">
+      <c r="J25" s="4" t="s">
         <v>172</v>
       </c>
-      <c r="G25" s="4" t="s">
+      <c r="K25" s="4" t="s">
         <v>173</v>
-      </c>
-      <c r="H25" s="4" t="s">
-        <v>174</v>
-      </c>
-      <c r="I25" s="4" t="s">
-        <v>175</v>
-      </c>
-      <c r="J25" s="4" t="s">
-        <v>176</v>
-      </c>
-      <c r="K25" s="4" t="s">
-        <v>177</v>
       </c>
     </row>
     <row r="26">
@@ -1760,36 +1748,36 @@
         <v>71</v>
       </c>
       <c r="C26" s="6" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D26" s="6" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E26" s="6" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F26" s="6" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G26" s="6" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="H26" s="6" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="I26" s="6" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="J26" s="6" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="K26" s="6" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="27" ht="62.5" customHeight="1">
       <c r="B27" s="11" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
     </row>
   </sheetData>
